--- a/reports/final_verified_leads.xlsx
+++ b/reports/final_verified_leads.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+919116135091</t>
+          <t>+91 91161 35108</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -776,11 +776,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -799,12 +799,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -971,11 +971,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>+91 99290 99748</t>
+          <t>+91 94140 71922</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -1044,17 +1044,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Laxmi Mishthan Bhandar, No</t>
+          <t>100-101, Johri Bazar, Bapu Bazar, Biseswarji, Jaipur, Rajasthan, 302003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+91 90246 09609</t>
+          <t>+91 9024609609</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Not found in current evidence</t>
+          <t>8 AM to 11 AM</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1101,35 +1101,35 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2, Gandhi Path W, Acharya Vinoba Bhave Nagar, B Block, Vaishali Nagar, Jaipur</t>
+          <t>Not confidently extracted</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>+91 86969 17580</t>
+          <t>+918696917580</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>08:00 AM - 10:30 PM</t>
+          <t>Closed ⋅ Opens 11AM Phone: 090244 47555</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -1231,11 +1231,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>STRONG WEB SUPPORT</t>
+          <t>REVIEW REQUIRED</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
+          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
         </is>
       </c>
     </row>
@@ -1361,35 +1361,35 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>STRONG WEB SUPPORT</t>
+          <t>REVIEW REQUIRED</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Station Road Jaipur</t>
+          <t>Rawat Public School Sector-17, Pratap Nagar, Sanganer Jaipur (Rajasthan)-302033 Email: rawatpublicschool100@gmail.com narendra702@gmail.com Call: 0141-2796929, +91 7300000875, +91 8058007777 ## Useful</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>+91 7300000875</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Not found in current evidence</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Not found in current evidence</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
+          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>107,108 AJMERA GARDEN, SAMRAT, KINGS ROAD, AJMER ROAD, Jaipur</t>
+          <t>Not confidently extracted</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1491,20 +1491,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Janta Store Shopping Centre, University Marg, Bapu Nagar, Jaipur, Rajasthan 302015 Google Map: Ph: 089528 93657 Pricing: Tandoori Pizza: Rs</t>
+          <t>Not confidently extracted</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+918949778386</t>
+          <t>+919664026168</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Not confidently extracted</t>
+          <t>Hotel Clarks Amer, Jawahar Lal Nehru Marg, Jaipur 302017 CONTACT:EMAIL | PHONE CUISINE:Multi-cuisine TabluPhoto courtesy: Hotel Clarks Amer HappyTrips Editors TABLU - Hotel Clarks Amer Jaipur, Jaipur.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>141-3610101</t>
+          <t>Not found in current evidence</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1751,20 +1751,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>(/cdn-cgi/l/email-protection)</t>
+          <t>Not confidently extracted</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>+919810372000</t>
+          <t>+919829166866</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>

--- a/reports/final_verified_leads.xlsx
+++ b/reports/final_verified_leads.xlsx
@@ -776,11 +776,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>STRONG WEB SUPPORT</t>
+          <t>REVIEW REQUIRED</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -799,12 +799,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
+          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
         </is>
       </c>
     </row>
@@ -1044,17 +1044,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100-101, Johri Bazar, Bapu Bazar, Biseswarji, Jaipur, Rajasthan, 302003</t>
+          <t>Laxmi Mishthan Bhandar, No. 98, 99, Johari Bazar Rd, Bapu Bazar, Biseswarji, Jaipur, Rajasthan 302 003; tel: +91 90246 09609</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+91 9024609609</t>
+          <t>+91 90246 09609</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8 AM to 11 AM</t>
+          <t>Not found in current evidence</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Closed ⋅ Opens 11AM Phone: 090244 47555</t>
+          <t>Closed ⋅ Opens 11AM Phone: 090244 47555 Mahaveer Rabri Bhandar</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12:00 PM to 10:00 PM</t>
+          <t>Not found in current evidence</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1231,11 +1231,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -1361,20 +1361,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Rawat Public School Sector-17, Pratap Nagar, Sanganer Jaipur (Rajasthan)-302033 Email: rawatpublicschool100@gmail.com narendra702@gmail.com Call: 0141-2796929, +91 7300000875, +91 8058007777 ## Useful</t>
+          <t>Tonk Road Jaipur</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>+91 7300000875</t>
+          <t>Not found in current evidence</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -1491,11 +1491,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>STRONG WEB SUPPORT</t>
+          <t>REVIEW REQUIRED</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>+919664026168</t>
+          <t>+918949778386</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
+          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Not found in current evidence</t>
+          <t>141-3610101</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">

--- a/reports/final_verified_leads.xlsx
+++ b/reports/final_verified_leads.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Not confidently extracted</t>
+          <t>Ajmer Road, Jaipur, Rajasthan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -776,11 +776,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>REVIEW REQUIRED</t>
+          <t>STRONG WEB SUPPORT</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -799,12 +799,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Multiple web sources were found, but at least one important field differs between sources. The conflicting field should be reviewed before treating the information as fully verified.</t>
+          <t>Multiple independent web sources provide supporting evidence with no major extracted-field conflict detected.</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tonk Road Jaipur</t>
+          <t>Not confidently extracted</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Not found in current evidence</t>
+          <t>0141-2170883</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Not confidently extracted</t>
+          <t>Janta Store Shopping Centre, University Marg, Bapu Nagar, Jaipur, Rajasthan 302015 Google Map: Ph: 089528 93657 Pricing: Tandoori Pizza: Rs.260 Egg Halwa: Rs.100 Watch Our Other Street Food Tours Mumb</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Not confidently extracted</t>
+          <t>Malviya Nagar Jaipur</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
